--- a/Unity/Assets/Config/Excel/Skill/ReactionConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Skill/ReactionConfig.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="331">
   <si>
     <t>Id</t>
   </si>
@@ -82,7 +82,7 @@
     <t>Duration</t>
   </si>
   <si>
-    <t>ApplyBuffs</t>
+    <t>BuffIds</t>
   </si>
   <si>
     <t>VfxName</t>
@@ -274,9 +274,6 @@
     <t>1.5</t>
   </si>
   <si>
-    <t>1001</t>
-  </si>
-  <si>
     <t>Vfx_Vaporize</t>
   </si>
   <si>
@@ -298,9 +295,6 @@
     <t>1.2</t>
   </si>
   <si>
-    <t>1002</t>
-  </si>
-  <si>
     <t>Vfx_Melt</t>
   </si>
   <si>
@@ -322,9 +316,6 @@
     <t>2.2</t>
   </si>
   <si>
-    <t>1003</t>
-  </si>
-  <si>
     <t>Vfx_Overload</t>
   </si>
   <si>
@@ -343,7 +334,7 @@
     <t>1.3</t>
   </si>
   <si>
-    <t>1004</t>
+    <t>257</t>
   </si>
   <si>
     <t>Vfx_ElectroCharged</t>
@@ -364,7 +355,7 @@
     <t>1.8</t>
   </si>
   <si>
-    <t>1005</t>
+    <t>12093</t>
   </si>
   <si>
     <t>Vfx_SuperConduct</t>
@@ -385,7 +376,7 @@
     <t>1.0</t>
   </si>
   <si>
-    <t>1006</t>
+    <t>261</t>
   </si>
   <si>
     <t>Vfx_Frozen</t>
@@ -403,9 +394,6 @@
     <t>风+火=火扩散</t>
   </si>
   <si>
-    <t>1007</t>
-  </si>
-  <si>
     <t>Vfx_Swirl_Fire</t>
   </si>
   <si>
@@ -415,9 +403,6 @@
     <t>风+水=水扩散</t>
   </si>
   <si>
-    <t>1008</t>
-  </si>
-  <si>
     <t>Vfx_Swirl_Water</t>
   </si>
   <si>
@@ -427,9 +412,6 @@
     <t>风+雷=雷扩散</t>
   </si>
   <si>
-    <t>1009</t>
-  </si>
-  <si>
     <t>Vfx_Swirl_Lightning</t>
   </si>
   <si>
@@ -439,9 +421,6 @@
     <t>风+冰=冰扩散</t>
   </si>
   <si>
-    <t>1010</t>
-  </si>
-  <si>
     <t>Vfx_Swirl_Ice</t>
   </si>
   <si>
@@ -451,9 +430,6 @@
     <t>土+火=结晶-火盾</t>
   </si>
   <si>
-    <t>1011</t>
-  </si>
-  <si>
     <t>Vfx_Crystallize_Fire</t>
   </si>
   <si>
@@ -463,9 +439,6 @@
     <t>土+水=结晶-水盾</t>
   </si>
   <si>
-    <t>1012</t>
-  </si>
-  <si>
     <t>Vfx_Crystallize_Water</t>
   </si>
   <si>
@@ -475,9 +448,6 @@
     <t>土+雷=结晶-雷盾</t>
   </si>
   <si>
-    <t>1013</t>
-  </si>
-  <si>
     <t>Vfx_Crystallize_Lightning</t>
   </si>
   <si>
@@ -487,9 +457,6 @@
     <t>土+冰=结晶-冰盾</t>
   </si>
   <si>
-    <t>1014</t>
-  </si>
-  <si>
     <t>Vfx_Crystallize_Ice</t>
   </si>
   <si>
@@ -499,9 +466,6 @@
     <t>火+毒=毒燃(毒扩散+持续伤)</t>
   </si>
   <si>
-    <t>1015</t>
-  </si>
-  <si>
     <t>Vfx_PoisonBurn</t>
   </si>
   <si>
@@ -520,9 +484,6 @@
     <t>19</t>
   </si>
   <si>
-    <t>1016</t>
-  </si>
-  <si>
     <t>Vfx_PoisonMist</t>
   </si>
   <si>
@@ -547,9 +508,6 @@
     <t>1.6</t>
   </si>
   <si>
-    <t>1017</t>
-  </si>
-  <si>
     <t>Vfx_Purify</t>
   </si>
   <si>
@@ -562,9 +520,6 @@
     <t>18</t>
   </si>
   <si>
-    <t>1018</t>
-  </si>
-  <si>
     <t>Vfx_Corrupt</t>
   </si>
   <si>
@@ -574,9 +529,6 @@
     <t>光+毒=净化解毒</t>
   </si>
   <si>
-    <t>1019</t>
-  </si>
-  <si>
     <t>Vfx_PurifyPoison</t>
   </si>
   <si>
@@ -586,9 +538,6 @@
     <t>暗+毒=剧毒强化</t>
   </si>
   <si>
-    <t>1020</t>
-  </si>
-  <si>
     <t>Vfx_DarkPoison</t>
   </si>
   <si>
@@ -673,9 +622,6 @@
     <t>1000</t>
   </si>
   <si>
-    <t>1021</t>
-  </si>
-  <si>
     <t>Vfx_OilExplosion</t>
   </si>
   <si>
@@ -694,9 +640,6 @@
     <t>500</t>
   </si>
   <si>
-    <t>1022</t>
-  </si>
-  <si>
     <t>Vfx_BombExplosion</t>
   </si>
   <si>
@@ -745,9 +688,6 @@
     <t>0.9</t>
   </si>
   <si>
-    <t>1023</t>
-  </si>
-  <si>
     <t>Vfx_WaterSoil</t>
   </si>
   <si>
@@ -775,9 +715,6 @@
     <t>水+沼泽材质=加深沼泽</t>
   </si>
   <si>
-    <t>1024</t>
-  </si>
-  <si>
     <t>Vfx_BogDeepen</t>
   </si>
   <si>
@@ -844,9 +781,6 @@
     <t>23</t>
   </si>
   <si>
-    <t>1025</t>
-  </si>
-  <si>
     <t>Vfx_MetalElectrify</t>
   </si>
   <si>
@@ -892,9 +826,6 @@
     <t>27</t>
   </si>
   <si>
-    <t>1026</t>
-  </si>
-  <si>
     <t>Vfx_SandBlow</t>
   </si>
   <si>
@@ -913,9 +844,6 @@
     <t>风+雪材质=暴风雪</t>
   </si>
   <si>
-    <t>1027</t>
-  </si>
-  <si>
     <t>Vfx_SnowBlizzard</t>
   </si>
   <si>
@@ -946,9 +874,6 @@
     <t>土+水材质=泥沼(困住)</t>
   </si>
   <si>
-    <t>1028</t>
-  </si>
-  <si>
     <t>Vfx_MudTrap</t>
   </si>
   <si>
@@ -988,9 +913,6 @@
     <t>毒+肉材质=剧毒侵蚀</t>
   </si>
   <si>
-    <t>1029</t>
-  </si>
-  <si>
     <t>Vfx_PoisonCorrode</t>
   </si>
   <si>
@@ -1009,9 +931,6 @@
     <t>毒+布材质=毒染</t>
   </si>
   <si>
-    <t>1030</t>
-  </si>
-  <si>
     <t>Vfx_ClothPoisoned</t>
   </si>
   <si>
@@ -1033,9 +952,6 @@
     <t>光+玻璃材质=折射(范围光伤)</t>
   </si>
   <si>
-    <t>1031</t>
-  </si>
-  <si>
     <t>Vfx_LightRefract</t>
   </si>
   <si>
@@ -1076,9 +992,6 @@
   </si>
   <si>
     <t>暗+结界=腐蚀结界</t>
-  </si>
-  <si>
-    <t>1032</t>
   </si>
   <si>
     <t>Vfx_BarrierCorrupt</t>
@@ -1100,7 +1013,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -1112,12 +1025,17 @@
       <name val="Helvetica Neue"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="15"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Helvetica"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1126,7 +1044,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="11"/>
+        <fgColor indexed="9"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="12"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -1141,13 +1065,103 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
       </left>
       <right style="thin">
         <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
       </top>
       <bottom style="thin">
         <color indexed="10"/>
@@ -1156,13 +1170,13 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="11"/>
       </top>
       <bottom style="thin">
         <color indexed="10"/>
@@ -1171,106 +1185,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="9"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
+        <color indexed="11"/>
       </left>
       <right style="thin">
         <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="11"/>
       </top>
       <bottom style="thin">
         <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="9"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1280,20 +1204,29 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -1305,25 +1238,22 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1343,6 +1273,7 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffadadad"/>
       <rgbColor rgb="ffe3e3e3"/>
       <rgbColor rgb="fff4f9f8"/>
@@ -2384,19 +2315,19 @@
   <sheetFormatPr defaultColWidth="8.33333" defaultRowHeight="15.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="2" width="8.35156" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.0938" style="1" customWidth="1"/>
-    <col min="4" max="4" width="24.4766" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1719" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.3516" style="1" customWidth="1"/>
     <col min="6" max="6" width="9.35156" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.8906" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.8516" style="1" customWidth="1"/>
     <col min="8" max="8" width="8.17188" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.48438" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5" style="1" customWidth="1"/>
     <col min="10" max="10" width="10.1719" style="1" customWidth="1"/>
     <col min="11" max="11" width="12.8516" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.9688" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.5625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9.91406" style="1" customWidth="1"/>
-    <col min="15" max="15" width="21.8984" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9.85156" style="1" customWidth="1"/>
+    <col min="15" max="15" width="21.8516" style="1" customWidth="1"/>
     <col min="16" max="16384" width="8.35156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3345,21 +3276,19 @@
       <c r="M26" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="N26" t="s" s="6">
+      <c r="N26" s="6"/>
+      <c r="O26" t="s" s="7">
         <v>87</v>
-      </c>
-      <c r="O26" t="s" s="7">
-        <v>88</v>
       </c>
     </row>
     <row r="27" ht="20.05" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="9"/>
       <c r="C27" t="s" s="9">
+        <v>88</v>
+      </c>
+      <c r="D27" t="s" s="9">
         <v>89</v>
-      </c>
-      <c r="D27" t="s" s="9">
-        <v>90</v>
       </c>
       <c r="E27" t="s" s="9">
         <v>41</v>
@@ -3388,21 +3317,19 @@
       <c r="M27" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="N27" t="s" s="9">
-        <v>87</v>
-      </c>
+      <c r="N27" s="9"/>
       <c r="O27" t="s" s="10">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" ht="20.05" customHeight="1">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" t="s" s="6">
+        <v>91</v>
+      </c>
+      <c r="D28" t="s" s="6">
         <v>92</v>
-      </c>
-      <c r="D28" t="s" s="6">
-        <v>93</v>
       </c>
       <c r="E28" t="s" s="6">
         <v>44</v>
@@ -3417,7 +3344,7 @@
         <v>37</v>
       </c>
       <c r="I28" t="s" s="6">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J28" t="s" s="6">
         <v>31</v>
@@ -3431,21 +3358,19 @@
       <c r="M28" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="N28" t="s" s="6">
-        <v>95</v>
-      </c>
+      <c r="N28" s="6"/>
       <c r="O28" t="s" s="7">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" ht="20.05" customHeight="1">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" t="s" s="9">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D29" t="s" s="9">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E29" t="s" s="9">
         <v>64</v>
@@ -3460,7 +3385,7 @@
         <v>37</v>
       </c>
       <c r="I29" t="s" s="9">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J29" t="s" s="9">
         <v>31</v>
@@ -3474,21 +3399,19 @@
       <c r="M29" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="N29" t="s" s="9">
-        <v>95</v>
-      </c>
+      <c r="N29" s="9"/>
       <c r="O29" t="s" s="10">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" ht="20.05" customHeight="1">
       <c r="A30" s="5"/>
       <c r="B30" s="6"/>
       <c r="C30" t="s" s="6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D30" t="s" s="6">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E30" t="s" s="6">
         <v>44</v>
@@ -3503,7 +3426,7 @@
         <v>33</v>
       </c>
       <c r="I30" t="s" s="6">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J30" t="s" s="6">
         <v>31</v>
@@ -3517,21 +3440,19 @@
       <c r="M30" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="N30" t="s" s="6">
-        <v>103</v>
-      </c>
+      <c r="N30" s="6"/>
       <c r="O30" t="s" s="7">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" ht="20.05" customHeight="1">
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" t="s" s="9">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D31" t="s" s="9">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E31" t="s" s="9">
         <v>51</v>
@@ -3546,7 +3467,7 @@
         <v>33</v>
       </c>
       <c r="I31" t="s" s="9">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J31" t="s" s="9">
         <v>31</v>
@@ -3560,21 +3481,19 @@
       <c r="M31" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="N31" t="s" s="9">
-        <v>103</v>
-      </c>
+      <c r="N31" s="9"/>
       <c r="O31" t="s" s="10">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" ht="20.05" customHeight="1">
       <c r="A32" s="5"/>
       <c r="B32" s="6"/>
       <c r="C32" t="s" s="6">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D32" t="s" s="6">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E32" t="s" s="6">
         <v>51</v>
@@ -3589,7 +3508,7 @@
         <v>41</v>
       </c>
       <c r="I32" t="s" s="6">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J32" t="s" s="6">
         <v>31</v>
@@ -3603,21 +3522,21 @@
       <c r="M32" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="N32" t="s" s="6">
-        <v>110</v>
+      <c r="N32" t="s" s="12">
+        <v>107</v>
       </c>
       <c r="O32" t="s" s="7">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" ht="20.05" customHeight="1">
       <c r="A33" s="8"/>
       <c r="B33" s="9"/>
       <c r="C33" t="s" s="9">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s" s="9">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E33" t="s" s="9">
         <v>41</v>
@@ -3632,7 +3551,7 @@
         <v>41</v>
       </c>
       <c r="I33" t="s" s="9">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J33" t="s" s="9">
         <v>31</v>
@@ -3646,21 +3565,21 @@
       <c r="M33" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="N33" t="s" s="9">
-        <v>110</v>
+      <c r="N33" t="s" s="13">
+        <v>107</v>
       </c>
       <c r="O33" t="s" s="10">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" ht="20.05" customHeight="1">
       <c r="A34" s="5"/>
       <c r="B34" s="6"/>
       <c r="C34" t="s" s="6">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D34" t="s" s="6">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E34" t="s" s="6">
         <v>51</v>
@@ -3675,7 +3594,7 @@
         <v>39</v>
       </c>
       <c r="I34" t="s" s="6">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J34" t="s" s="6">
         <v>31</v>
@@ -3690,20 +3609,20 @@
         <v>36</v>
       </c>
       <c r="N34" t="s" s="6">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="O34" t="s" s="7">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" ht="20.05" customHeight="1">
       <c r="A35" s="8"/>
       <c r="B35" s="9"/>
       <c r="C35" t="s" s="9">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D35" t="s" s="9">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E35" t="s" s="9">
         <v>64</v>
@@ -3718,7 +3637,7 @@
         <v>39</v>
       </c>
       <c r="I35" t="s" s="9">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J35" t="s" s="9">
         <v>31</v>
@@ -3733,20 +3652,20 @@
         <v>36</v>
       </c>
       <c r="N35" t="s" s="9">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="O35" t="s" s="10">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" ht="20.05" customHeight="1">
       <c r="A36" s="5"/>
       <c r="B36" s="6"/>
       <c r="C36" t="s" s="6">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D36" t="s" s="6">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E36" t="s" s="6">
         <v>64</v>
@@ -3761,7 +3680,7 @@
         <v>46</v>
       </c>
       <c r="I36" t="s" s="6">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J36" t="s" s="6">
         <v>31</v>
@@ -3775,21 +3694,21 @@
       <c r="M36" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="N36" t="s" s="6">
-        <v>124</v>
+      <c r="N36" t="s" s="12">
+        <v>121</v>
       </c>
       <c r="O36" t="s" s="7">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" ht="20.05" customHeight="1">
       <c r="A37" s="8"/>
       <c r="B37" s="9"/>
       <c r="C37" t="s" s="9">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D37" t="s" s="9">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E37" t="s" s="9">
         <v>41</v>
@@ -3804,7 +3723,7 @@
         <v>46</v>
       </c>
       <c r="I37" t="s" s="9">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J37" t="s" s="9">
         <v>31</v>
@@ -3818,21 +3737,21 @@
       <c r="M37" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="N37" t="s" s="9">
-        <v>124</v>
+      <c r="N37" t="s" s="13">
+        <v>121</v>
       </c>
       <c r="O37" t="s" s="10">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" ht="20.05" customHeight="1">
       <c r="A38" s="5"/>
       <c r="B38" s="6"/>
       <c r="C38" t="s" s="6">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D38" t="s" s="6">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E38" t="s" s="6">
         <v>35</v>
@@ -3847,7 +3766,7 @@
         <v>51</v>
       </c>
       <c r="I38" t="s" s="6">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J38" t="s" s="6">
         <v>31</v>
@@ -3861,21 +3780,19 @@
       <c r="M38" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="N38" t="s" s="6">
-        <v>130</v>
-      </c>
+      <c r="N38" s="6"/>
       <c r="O38" t="s" s="7">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39" ht="20.05" customHeight="1">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
       <c r="C39" t="s" s="9">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D39" t="s" s="9">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E39" t="s" s="9">
         <v>35</v>
@@ -3890,7 +3807,7 @@
         <v>51</v>
       </c>
       <c r="I39" t="s" s="9">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J39" t="s" s="9">
         <v>31</v>
@@ -3904,21 +3821,19 @@
       <c r="M39" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="N39" t="s" s="9">
-        <v>134</v>
-      </c>
+      <c r="N39" s="9"/>
       <c r="O39" t="s" s="10">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" ht="20.05" customHeight="1">
       <c r="A40" s="5"/>
       <c r="B40" s="6"/>
       <c r="C40" t="s" s="6">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D40" t="s" s="6">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E40" t="s" s="6">
         <v>35</v>
@@ -3933,7 +3848,7 @@
         <v>51</v>
       </c>
       <c r="I40" t="s" s="6">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J40" t="s" s="6">
         <v>31</v>
@@ -3947,21 +3862,19 @@
       <c r="M40" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="N40" t="s" s="6">
-        <v>138</v>
-      </c>
+      <c r="N40" s="6"/>
       <c r="O40" t="s" s="7">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" ht="20.05" customHeight="1">
       <c r="A41" s="8"/>
       <c r="B41" s="9"/>
       <c r="C41" t="s" s="9">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D41" t="s" s="9">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E41" t="s" s="9">
         <v>35</v>
@@ -3976,7 +3889,7 @@
         <v>51</v>
       </c>
       <c r="I41" t="s" s="9">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J41" t="s" s="9">
         <v>31</v>
@@ -3990,21 +3903,19 @@
       <c r="M41" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="N41" t="s" s="9">
-        <v>142</v>
-      </c>
+      <c r="N41" s="9"/>
       <c r="O41" t="s" s="10">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" ht="20.05" customHeight="1">
       <c r="A42" s="5"/>
       <c r="B42" s="6"/>
       <c r="C42" t="s" s="6">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D42" t="s" s="6">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E42" t="s" s="6">
         <v>46</v>
@@ -4019,7 +3930,7 @@
         <v>42</v>
       </c>
       <c r="I42" t="s" s="6">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J42" t="s" s="6">
         <v>31</v>
@@ -4033,21 +3944,19 @@
       <c r="M42" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="N42" t="s" s="6">
-        <v>146</v>
-      </c>
+      <c r="N42" s="6"/>
       <c r="O42" t="s" s="7">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" ht="20.05" customHeight="1">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" t="s" s="9">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D43" t="s" s="9">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E43" t="s" s="9">
         <v>46</v>
@@ -4062,7 +3971,7 @@
         <v>42</v>
       </c>
       <c r="I43" t="s" s="9">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J43" t="s" s="9">
         <v>31</v>
@@ -4076,21 +3985,19 @@
       <c r="M43" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="N43" t="s" s="9">
-        <v>150</v>
-      </c>
+      <c r="N43" s="9"/>
       <c r="O43" t="s" s="10">
-        <v>151</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" ht="20.05" customHeight="1">
       <c r="A44" s="5"/>
       <c r="B44" s="6"/>
       <c r="C44" t="s" s="6">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D44" t="s" s="6">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E44" t="s" s="6">
         <v>46</v>
@@ -4105,7 +4012,7 @@
         <v>42</v>
       </c>
       <c r="I44" t="s" s="6">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J44" t="s" s="6">
         <v>31</v>
@@ -4119,21 +4026,19 @@
       <c r="M44" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="N44" t="s" s="6">
-        <v>154</v>
-      </c>
+      <c r="N44" s="6"/>
       <c r="O44" t="s" s="7">
-        <v>155</v>
+        <v>145</v>
       </c>
     </row>
     <row r="45" ht="20.05" customHeight="1">
       <c r="A45" s="8"/>
       <c r="B45" s="9"/>
       <c r="C45" t="s" s="9">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D45" t="s" s="9">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E45" t="s" s="9">
         <v>46</v>
@@ -4148,7 +4053,7 @@
         <v>42</v>
       </c>
       <c r="I45" t="s" s="9">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J45" t="s" s="9">
         <v>31</v>
@@ -4162,21 +4067,19 @@
       <c r="M45" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="N45" t="s" s="9">
-        <v>158</v>
-      </c>
+      <c r="N45" s="9"/>
       <c r="O45" t="s" s="10">
-        <v>159</v>
+        <v>148</v>
       </c>
     </row>
     <row r="46" ht="20.05" customHeight="1">
       <c r="A46" s="5"/>
       <c r="B46" s="6"/>
       <c r="C46" t="s" s="6">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D46" t="s" s="6">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="E46" t="s" s="6">
         <v>44</v>
@@ -4205,21 +4108,19 @@
       <c r="M46" t="s" s="6">
         <v>62</v>
       </c>
-      <c r="N46" t="s" s="6">
-        <v>162</v>
-      </c>
+      <c r="N46" s="6"/>
       <c r="O46" t="s" s="7">
-        <v>163</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" ht="20.05" customHeight="1">
       <c r="A47" s="8"/>
       <c r="B47" s="9"/>
       <c r="C47" t="s" s="9">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D47" t="s" s="9">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E47" t="s" s="9">
         <v>58</v>
@@ -4248,21 +4149,19 @@
       <c r="M47" t="s" s="9">
         <v>62</v>
       </c>
-      <c r="N47" t="s" s="9">
-        <v>162</v>
-      </c>
+      <c r="N47" s="9"/>
       <c r="O47" t="s" s="10">
-        <v>163</v>
+        <v>151</v>
       </c>
     </row>
     <row r="48" ht="20.05" customHeight="1">
       <c r="A48" s="5"/>
       <c r="B48" s="6"/>
       <c r="C48" t="s" s="6">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D48" t="s" s="6">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E48" t="s" s="6">
         <v>41</v>
@@ -4274,10 +4173,10 @@
         <v>34</v>
       </c>
       <c r="H48" t="s" s="6">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I48" t="s" s="6">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J48" t="s" s="6">
         <v>31</v>
@@ -4291,21 +4190,19 @@
       <c r="M48" t="s" s="6">
         <v>59</v>
       </c>
-      <c r="N48" t="s" s="6">
-        <v>169</v>
-      </c>
+      <c r="N48" s="6"/>
       <c r="O48" t="s" s="7">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="49" ht="20.05" customHeight="1">
       <c r="A49" s="8"/>
       <c r="B49" s="9"/>
       <c r="C49" t="s" s="9">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="D49" t="s" s="9">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="E49" t="s" s="9">
         <v>58</v>
@@ -4317,10 +4214,10 @@
         <v>34</v>
       </c>
       <c r="H49" t="s" s="9">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I49" t="s" s="9">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J49" t="s" s="9">
         <v>31</v>
@@ -4334,11 +4231,9 @@
       <c r="M49" t="s" s="9">
         <v>59</v>
       </c>
-      <c r="N49" t="s" s="9">
-        <v>169</v>
-      </c>
+      <c r="N49" s="9"/>
       <c r="O49" t="s" s="10">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" ht="20.05" customHeight="1">
@@ -4347,7 +4242,7 @@
         <v>29</v>
       </c>
       <c r="C50" t="s" s="6">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
@@ -4366,10 +4261,10 @@
       <c r="A51" s="8"/>
       <c r="B51" s="9"/>
       <c r="C51" t="s" s="9">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="D51" t="s" s="9">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="E51" t="s" s="9">
         <v>42</v>
@@ -4381,10 +4276,10 @@
         <v>34</v>
       </c>
       <c r="H51" t="s" s="9">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="I51" t="s" s="9">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="J51" t="s" s="9">
         <v>31</v>
@@ -4398,21 +4293,19 @@
       <c r="M51" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="N51" t="s" s="9">
-        <v>178</v>
-      </c>
+      <c r="N51" s="9"/>
       <c r="O51" t="s" s="10">
-        <v>179</v>
+        <v>165</v>
       </c>
     </row>
     <row r="52" ht="20.05" customHeight="1">
       <c r="A52" s="5"/>
       <c r="B52" s="6"/>
       <c r="C52" t="s" s="6">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="D52" t="s" s="6">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="E52" t="s" s="6">
         <v>56</v>
@@ -4424,10 +4317,10 @@
         <v>34</v>
       </c>
       <c r="H52" t="s" s="6">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="I52" t="s" s="6">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="J52" t="s" s="6">
         <v>31</v>
@@ -4441,21 +4334,19 @@
       <c r="M52" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="N52" t="s" s="6">
-        <v>183</v>
-      </c>
+      <c r="N52" s="6"/>
       <c r="O52" t="s" s="7">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53" ht="20.05" customHeight="1">
       <c r="A53" s="8"/>
       <c r="B53" s="9"/>
       <c r="C53" t="s" s="9">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="D53" t="s" s="9">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="E53" t="s" s="9">
         <v>42</v>
@@ -4467,7 +4358,7 @@
         <v>34</v>
       </c>
       <c r="H53" t="s" s="9">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="I53" t="s" s="9">
         <v>86</v>
@@ -4484,21 +4375,19 @@
       <c r="M53" t="s" s="9">
         <v>52</v>
       </c>
-      <c r="N53" t="s" s="9">
-        <v>187</v>
-      </c>
+      <c r="N53" s="9"/>
       <c r="O53" t="s" s="10">
-        <v>188</v>
+        <v>172</v>
       </c>
     </row>
     <row r="54" ht="20.05" customHeight="1">
       <c r="A54" s="5"/>
       <c r="B54" s="6"/>
       <c r="C54" t="s" s="6">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="D54" t="s" s="6">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="E54" t="s" s="6">
         <v>56</v>
@@ -4510,10 +4399,10 @@
         <v>34</v>
       </c>
       <c r="H54" t="s" s="6">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I54" t="s" s="6">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J54" t="s" s="6">
         <v>31</v>
@@ -4527,20 +4416,18 @@
       <c r="M54" t="s" s="6">
         <v>59</v>
       </c>
-      <c r="N54" t="s" s="6">
-        <v>191</v>
-      </c>
+      <c r="N54" s="6"/>
       <c r="O54" t="s" s="7">
-        <v>192</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55" ht="20.05" customHeight="1">
       <c r="A55" s="8"/>
       <c r="B55" t="s" s="9">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="C55" t="s" s="9">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
@@ -4561,7 +4448,7 @@
         <v>29</v>
       </c>
       <c r="C56" t="s" s="6">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
@@ -4580,10 +4467,10 @@
       <c r="A57" s="8"/>
       <c r="B57" s="9"/>
       <c r="C57" t="s" s="9">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="D57" t="s" s="9">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="E57" t="s" s="9">
         <v>44</v>
@@ -4595,10 +4482,10 @@
         <v>31</v>
       </c>
       <c r="H57" t="s" s="9">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="I57" t="s" s="9">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J57" t="s" s="9">
         <v>31</v>
@@ -4610,23 +4497,21 @@
         <v>48</v>
       </c>
       <c r="M57" t="s" s="9">
-        <v>199</v>
-      </c>
-      <c r="N57" t="s" s="9">
-        <v>110</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N57" s="9"/>
       <c r="O57" t="s" s="10">
-        <v>200</v>
+        <v>183</v>
       </c>
     </row>
     <row r="58" ht="20.05" customHeight="1">
       <c r="A58" s="5"/>
       <c r="B58" s="6"/>
       <c r="C58" t="s" s="6">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="D58" t="s" s="6">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="E58" t="s" s="6">
         <v>44</v>
@@ -4638,10 +4523,10 @@
         <v>31</v>
       </c>
       <c r="H58" t="s" s="6">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="I58" t="s" s="6">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J58" t="s" s="6">
         <v>31</v>
@@ -4650,26 +4535,24 @@
         <v>34</v>
       </c>
       <c r="L58" t="s" s="6">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="M58" t="s" s="6">
-        <v>199</v>
-      </c>
-      <c r="N58" t="s" s="6">
-        <v>110</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N58" s="6"/>
       <c r="O58" t="s" s="7">
-        <v>204</v>
+        <v>187</v>
       </c>
     </row>
     <row r="59" ht="20.05" customHeight="1">
       <c r="A59" s="8"/>
       <c r="B59" s="9"/>
       <c r="C59" t="s" s="9">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="D59" t="s" s="9">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="E59" t="s" s="9">
         <v>44</v>
@@ -4681,10 +4564,10 @@
         <v>31</v>
       </c>
       <c r="H59" t="s" s="9">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="I59" t="s" s="9">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="J59" t="s" s="9">
         <v>31</v>
@@ -4696,23 +4579,21 @@
         <v>58</v>
       </c>
       <c r="M59" t="s" s="9">
-        <v>199</v>
-      </c>
-      <c r="N59" t="s" s="9">
-        <v>110</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N59" s="9"/>
       <c r="O59" t="s" s="10">
-        <v>208</v>
+        <v>191</v>
       </c>
     </row>
     <row r="60" ht="20.05" customHeight="1">
       <c r="A60" s="5"/>
       <c r="B60" s="6"/>
       <c r="C60" t="s" s="6">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="D60" t="s" s="6">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="E60" t="s" s="6">
         <v>44</v>
@@ -4724,10 +4605,10 @@
         <v>31</v>
       </c>
       <c r="H60" t="s" s="6">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="I60" t="s" s="6">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J60" t="s" s="6">
         <v>31</v>
@@ -4743,17 +4624,17 @@
       </c>
       <c r="N60" s="6"/>
       <c r="O60" t="s" s="7">
-        <v>212</v>
+        <v>195</v>
       </c>
     </row>
     <row r="61" ht="20.05" customHeight="1">
       <c r="A61" s="8"/>
       <c r="B61" s="9"/>
       <c r="C61" t="s" s="9">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="D61" t="s" s="9">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="E61" t="s" s="9">
         <v>44</v>
@@ -4765,10 +4646,10 @@
         <v>31</v>
       </c>
       <c r="H61" t="s" s="9">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="I61" t="s" s="9">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J61" t="s" s="9">
         <v>31</v>
@@ -4784,17 +4665,17 @@
       </c>
       <c r="N61" s="9"/>
       <c r="O61" t="s" s="10">
-        <v>215</v>
+        <v>198</v>
       </c>
     </row>
     <row r="62" ht="20.05" customHeight="1">
       <c r="A62" s="5"/>
       <c r="B62" s="6"/>
       <c r="C62" t="s" s="6">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="D62" t="s" s="6">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="E62" t="s" s="6">
         <v>44</v>
@@ -4806,53 +4687,51 @@
         <v>31</v>
       </c>
       <c r="H62" t="s" s="6">
+        <v>186</v>
+      </c>
+      <c r="I62" t="s" s="6">
+        <v>201</v>
+      </c>
+      <c r="J62" t="s" s="6">
+        <v>31</v>
+      </c>
+      <c r="K62" t="s" s="6">
+        <v>34</v>
+      </c>
+      <c r="L62" t="s" s="6">
+        <v>34</v>
+      </c>
+      <c r="M62" t="s" s="6">
+        <v>202</v>
+      </c>
+      <c r="N62" s="6"/>
+      <c r="O62" t="s" s="7">
         <v>203</v>
-      </c>
-      <c r="I62" t="s" s="6">
-        <v>218</v>
-      </c>
-      <c r="J62" t="s" s="6">
-        <v>31</v>
-      </c>
-      <c r="K62" t="s" s="6">
-        <v>34</v>
-      </c>
-      <c r="L62" t="s" s="6">
-        <v>34</v>
-      </c>
-      <c r="M62" t="s" s="6">
-        <v>219</v>
-      </c>
-      <c r="N62" t="s" s="6">
-        <v>220</v>
-      </c>
-      <c r="O62" t="s" s="7">
-        <v>221</v>
       </c>
     </row>
     <row r="63" ht="20.05" customHeight="1">
       <c r="A63" s="8"/>
       <c r="B63" s="9"/>
       <c r="C63" t="s" s="9">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="D63" t="s" s="9">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="E63" t="s" s="9">
         <v>44</v>
       </c>
       <c r="F63" t="s" s="9">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="G63" t="s" s="9">
         <v>31</v>
       </c>
       <c r="H63" t="s" s="9">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="I63" t="s" s="9">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="J63" t="s" s="9">
         <v>31</v>
@@ -4864,38 +4743,36 @@
         <v>34</v>
       </c>
       <c r="M63" t="s" s="9">
-        <v>226</v>
-      </c>
-      <c r="N63" t="s" s="9">
-        <v>227</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N63" s="9"/>
       <c r="O63" t="s" s="10">
-        <v>228</v>
+        <v>209</v>
       </c>
     </row>
     <row r="64" ht="20.05" customHeight="1">
       <c r="A64" s="5"/>
       <c r="B64" s="6"/>
       <c r="C64" t="s" s="6">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="D64" t="s" s="6">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="E64" t="s" s="6">
         <v>44</v>
       </c>
       <c r="F64" t="s" s="6">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="G64" t="s" s="6">
         <v>31</v>
       </c>
       <c r="H64" t="s" s="6">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="I64" t="s" s="6">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="J64" t="s" s="6">
         <v>31</v>
@@ -4911,32 +4788,32 @@
       </c>
       <c r="N64" s="6"/>
       <c r="O64" t="s" s="7">
-        <v>233</v>
+        <v>214</v>
       </c>
     </row>
     <row r="65" ht="20.05" customHeight="1">
       <c r="A65" s="8"/>
       <c r="B65" s="9"/>
       <c r="C65" t="s" s="9">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="D65" t="s" s="9">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="E65" t="s" s="9">
         <v>44</v>
       </c>
       <c r="F65" t="s" s="9">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="G65" t="s" s="9">
         <v>31</v>
       </c>
       <c r="H65" t="s" s="9">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="I65" t="s" s="9">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J65" t="s" s="9">
         <v>31</v>
@@ -4952,17 +4829,17 @@
       </c>
       <c r="N65" s="9"/>
       <c r="O65" t="s" s="10">
-        <v>236</v>
+        <v>217</v>
       </c>
     </row>
     <row r="66" ht="20.05" customHeight="1">
       <c r="A66" s="5"/>
       <c r="B66" s="6"/>
       <c r="C66" t="s" s="6">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="D66" t="s" s="6">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="E66" t="s" s="6">
         <v>44</v>
@@ -4974,16 +4851,16 @@
         <v>31</v>
       </c>
       <c r="H66" t="s" s="6">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="I66" t="s" s="6">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J66" t="s" s="6">
         <v>31</v>
       </c>
       <c r="K66" t="s" s="6">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="L66" t="s" s="6">
         <v>41</v>
@@ -4993,7 +4870,7 @@
       </c>
       <c r="N66" s="6"/>
       <c r="O66" t="s" s="7">
-        <v>239</v>
+        <v>220</v>
       </c>
     </row>
     <row r="67" ht="20.05" customHeight="1">
@@ -5002,7 +4879,7 @@
         <v>29</v>
       </c>
       <c r="C67" t="s" s="9">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="D67" s="9"/>
       <c r="E67" s="9"/>
@@ -5021,10 +4898,10 @@
       <c r="A68" s="5"/>
       <c r="B68" s="6"/>
       <c r="C68" t="s" s="6">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="D68" t="s" s="6">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="E68" t="s" s="6">
         <v>41</v>
@@ -5039,7 +4916,7 @@
         <v>64</v>
       </c>
       <c r="I68" t="s" s="6">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="J68" t="s" s="6">
         <v>31</v>
@@ -5053,21 +4930,19 @@
       <c r="M68" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="N68" t="s" s="6">
-        <v>244</v>
-      </c>
+      <c r="N68" s="6"/>
       <c r="O68" t="s" s="7">
-        <v>245</v>
+        <v>225</v>
       </c>
     </row>
     <row r="69" ht="20.05" customHeight="1">
       <c r="A69" s="8"/>
       <c r="B69" s="9"/>
       <c r="C69" t="s" s="9">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="D69" t="s" s="9">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="E69" t="s" s="9">
         <v>41</v>
@@ -5082,7 +4957,7 @@
         <v>64</v>
       </c>
       <c r="I69" t="s" s="9">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="J69" t="s" s="9">
         <v>31</v>
@@ -5096,21 +4971,19 @@
       <c r="M69" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="N69" t="s" s="9">
-        <v>244</v>
-      </c>
+      <c r="N69" s="9"/>
       <c r="O69" t="s" s="10">
-        <v>248</v>
+        <v>228</v>
       </c>
     </row>
     <row r="70" ht="20.05" customHeight="1">
       <c r="A70" s="5"/>
       <c r="B70" s="6"/>
       <c r="C70" t="s" s="6">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="D70" t="s" s="6">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E70" t="s" s="6">
         <v>41</v>
@@ -5125,7 +4998,7 @@
         <v>64</v>
       </c>
       <c r="I70" t="s" s="6">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="J70" t="s" s="6">
         <v>31</v>
@@ -5139,21 +5012,19 @@
       <c r="M70" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="N70" t="s" s="6">
-        <v>244</v>
-      </c>
+      <c r="N70" s="6"/>
       <c r="O70" t="s" s="7">
-        <v>251</v>
+        <v>231</v>
       </c>
     </row>
     <row r="71" ht="20.05" customHeight="1">
       <c r="A71" s="8"/>
       <c r="B71" s="9"/>
       <c r="C71" t="s" s="9">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="D71" t="s" s="9">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="E71" t="s" s="9">
         <v>41</v>
@@ -5165,10 +5036,10 @@
         <v>31</v>
       </c>
       <c r="H71" t="s" s="9">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I71" t="s" s="9">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J71" t="s" s="9">
         <v>31</v>
@@ -5182,21 +5053,19 @@
       <c r="M71" t="s" s="9">
         <v>34</v>
       </c>
-      <c r="N71" t="s" s="9">
-        <v>254</v>
-      </c>
+      <c r="N71" s="9"/>
       <c r="O71" t="s" s="10">
-        <v>255</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72" ht="20.05" customHeight="1">
       <c r="A72" s="5"/>
       <c r="B72" s="6"/>
       <c r="C72" t="s" s="6">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="D72" t="s" s="6">
-        <v>257</v>
+        <v>236</v>
       </c>
       <c r="E72" t="s" s="6">
         <v>41</v>
@@ -5208,10 +5077,10 @@
         <v>31</v>
       </c>
       <c r="H72" t="s" s="6">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="I72" t="s" s="6">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="J72" t="s" s="6">
         <v>31</v>
@@ -5223,11 +5092,11 @@
         <v>34</v>
       </c>
       <c r="M72" t="s" s="6">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="N72" s="6"/>
       <c r="O72" t="s" s="7">
-        <v>260</v>
+        <v>239</v>
       </c>
     </row>
     <row r="73" ht="20.05" customHeight="1">
@@ -5236,7 +5105,7 @@
         <v>29</v>
       </c>
       <c r="C73" t="s" s="9">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
@@ -5255,10 +5124,10 @@
       <c r="A74" s="5"/>
       <c r="B74" s="6"/>
       <c r="C74" t="s" s="6">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="D74" t="s" s="6">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="E74" t="s" s="6">
         <v>64</v>
@@ -5270,10 +5139,10 @@
         <v>31</v>
       </c>
       <c r="H74" t="s" s="6">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="I74" t="s" s="6">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J74" t="s" s="6">
         <v>31</v>
@@ -5287,21 +5156,19 @@
       <c r="M74" t="s" s="6">
         <v>59</v>
       </c>
-      <c r="N74" t="s" s="6">
-        <v>124</v>
-      </c>
+      <c r="N74" s="6"/>
       <c r="O74" t="s" s="7">
-        <v>265</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75" ht="20.05" customHeight="1">
       <c r="A75" s="8"/>
       <c r="B75" s="9"/>
       <c r="C75" t="s" s="9">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="D75" t="s" s="9">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="E75" t="s" s="9">
         <v>64</v>
@@ -5316,7 +5183,7 @@
         <v>46</v>
       </c>
       <c r="I75" t="s" s="9">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J75" t="s" s="9">
         <v>31</v>
@@ -5330,27 +5197,25 @@
       <c r="M75" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="N75" t="s" s="9">
-        <v>124</v>
-      </c>
+      <c r="N75" s="9"/>
       <c r="O75" t="s" s="10">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="76" ht="20.05" customHeight="1">
       <c r="A76" s="5"/>
       <c r="B76" s="6"/>
       <c r="C76" t="s" s="6">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="D76" t="s" s="6">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="E76" t="s" s="6">
         <v>64</v>
       </c>
       <c r="F76" t="s" s="6">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="G76" t="s" s="6">
         <v>31</v>
@@ -5359,7 +5224,7 @@
         <v>46</v>
       </c>
       <c r="I76" t="s" s="6">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="J76" t="s" s="6">
         <v>31</v>
@@ -5375,7 +5240,7 @@
       </c>
       <c r="N76" s="6"/>
       <c r="O76" t="s" s="7">
-        <v>272</v>
+        <v>251</v>
       </c>
     </row>
     <row r="77" ht="20.05" customHeight="1">
@@ -5384,7 +5249,7 @@
         <v>29</v>
       </c>
       <c r="C77" t="s" s="9">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="D77" s="9"/>
       <c r="E77" s="9"/>
@@ -5403,10 +5268,10 @@
       <c r="A78" s="5"/>
       <c r="B78" s="6"/>
       <c r="C78" t="s" s="6">
-        <v>274</v>
+        <v>253</v>
       </c>
       <c r="D78" t="s" s="6">
-        <v>275</v>
+        <v>254</v>
       </c>
       <c r="E78" t="s" s="6">
         <v>51</v>
@@ -5418,7 +5283,7 @@
         <v>31</v>
       </c>
       <c r="H78" t="s" s="6">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="I78" t="s" s="6">
         <v>86</v>
@@ -5435,21 +5300,19 @@
       <c r="M78" t="s" s="6">
         <v>52</v>
       </c>
-      <c r="N78" t="s" s="6">
-        <v>277</v>
-      </c>
+      <c r="N78" s="6"/>
       <c r="O78" t="s" s="7">
-        <v>278</v>
+        <v>256</v>
       </c>
     </row>
     <row r="79" ht="20.05" customHeight="1">
       <c r="A79" s="8"/>
       <c r="B79" s="9"/>
       <c r="C79" t="s" s="9">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="D79" t="s" s="9">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="E79" t="s" s="9">
         <v>51</v>
@@ -5461,10 +5324,10 @@
         <v>31</v>
       </c>
       <c r="H79" t="s" s="9">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="I79" t="s" s="9">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J79" t="s" s="9">
         <v>31</v>
@@ -5478,21 +5341,19 @@
       <c r="M79" t="s" s="9">
         <v>52</v>
       </c>
-      <c r="N79" t="s" s="9">
-        <v>277</v>
-      </c>
+      <c r="N79" s="9"/>
       <c r="O79" t="s" s="10">
-        <v>281</v>
+        <v>259</v>
       </c>
     </row>
     <row r="80" ht="20.05" customHeight="1">
       <c r="A80" s="5"/>
       <c r="B80" s="6"/>
       <c r="C80" t="s" s="6">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s" s="6">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="E80" t="s" s="6">
         <v>51</v>
@@ -5504,10 +5365,10 @@
         <v>31</v>
       </c>
       <c r="H80" t="s" s="6">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="I80" t="s" s="6">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="J80" t="s" s="6">
         <v>31</v>
@@ -5521,27 +5382,25 @@
       <c r="M80" t="s" s="6">
         <v>52</v>
       </c>
-      <c r="N80" t="s" s="6">
-        <v>277</v>
-      </c>
+      <c r="N80" s="6"/>
       <c r="O80" t="s" s="7">
-        <v>284</v>
+        <v>262</v>
       </c>
     </row>
     <row r="81" ht="20.05" customHeight="1">
       <c r="A81" s="8"/>
       <c r="B81" s="9"/>
       <c r="C81" t="s" s="9">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="D81" t="s" s="9">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="E81" t="s" s="9">
         <v>51</v>
       </c>
       <c r="F81" t="s" s="9">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="G81" t="s" s="9">
         <v>31</v>
@@ -5550,7 +5409,7 @@
         <v>34</v>
       </c>
       <c r="I81" t="s" s="9">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="J81" t="s" s="9">
         <v>34</v>
@@ -5566,7 +5425,7 @@
       </c>
       <c r="N81" s="9"/>
       <c r="O81" t="s" s="10">
-        <v>288</v>
+        <v>266</v>
       </c>
     </row>
     <row r="82" ht="20.05" customHeight="1">
@@ -5575,7 +5434,7 @@
         <v>29</v>
       </c>
       <c r="C82" t="s" s="6">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
@@ -5594,10 +5453,10 @@
       <c r="A83" s="8"/>
       <c r="B83" s="9"/>
       <c r="C83" t="s" s="9">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="D83" t="s" s="9">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="E83" t="s" s="9">
         <v>35</v>
@@ -5609,10 +5468,10 @@
         <v>31</v>
       </c>
       <c r="H83" t="s" s="9">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="I83" t="s" s="9">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J83" t="s" s="9">
         <v>31</v>
@@ -5626,21 +5485,19 @@
       <c r="M83" t="s" s="9">
         <v>52</v>
       </c>
-      <c r="N83" t="s" s="9">
-        <v>293</v>
-      </c>
+      <c r="N83" s="9"/>
       <c r="O83" t="s" s="10">
-        <v>294</v>
+        <v>271</v>
       </c>
     </row>
     <row r="84" ht="20.05" customHeight="1">
       <c r="A84" s="5"/>
       <c r="B84" s="6"/>
       <c r="C84" t="s" s="6">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="D84" t="s" s="6">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="E84" t="s" s="6">
         <v>35</v>
@@ -5652,10 +5509,10 @@
         <v>31</v>
       </c>
       <c r="H84" t="s" s="6">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="I84" t="s" s="6">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J84" t="s" s="6">
         <v>31</v>
@@ -5669,21 +5526,19 @@
       <c r="M84" t="s" s="6">
         <v>52</v>
       </c>
-      <c r="N84" t="s" s="6">
-        <v>293</v>
-      </c>
+      <c r="N84" s="6"/>
       <c r="O84" t="s" s="7">
-        <v>297</v>
+        <v>274</v>
       </c>
     </row>
     <row r="85" ht="20.05" customHeight="1">
       <c r="A85" s="8"/>
       <c r="B85" s="9"/>
       <c r="C85" t="s" s="9">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="D85" t="s" s="9">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="E85" t="s" s="9">
         <v>35</v>
@@ -5695,10 +5550,10 @@
         <v>31</v>
       </c>
       <c r="H85" t="s" s="9">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="I85" t="s" s="9">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="J85" t="s" s="9">
         <v>31</v>
@@ -5712,21 +5567,19 @@
       <c r="M85" t="s" s="9">
         <v>52</v>
       </c>
-      <c r="N85" t="s" s="9">
-        <v>300</v>
-      </c>
+      <c r="N85" s="9"/>
       <c r="O85" t="s" s="10">
-        <v>301</v>
+        <v>277</v>
       </c>
     </row>
     <row r="86" ht="20.05" customHeight="1">
       <c r="A86" s="5"/>
       <c r="B86" s="6"/>
       <c r="C86" t="s" s="6">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="D86" t="s" s="6">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="E86" t="s" s="6">
         <v>35</v>
@@ -5738,10 +5591,10 @@
         <v>31</v>
       </c>
       <c r="H86" t="s" s="6">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="I86" t="s" s="6">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J86" t="s" s="6">
         <v>31</v>
@@ -5755,36 +5608,34 @@
       <c r="M86" t="s" s="6">
         <v>36</v>
       </c>
-      <c r="N86" t="s" s="6">
-        <v>300</v>
-      </c>
+      <c r="N86" s="6"/>
       <c r="O86" t="s" s="7">
-        <v>304</v>
+        <v>280</v>
       </c>
     </row>
     <row r="87" ht="20.05" customHeight="1">
       <c r="A87" s="8"/>
       <c r="B87" s="9"/>
       <c r="C87" t="s" s="9">
-        <v>305</v>
+        <v>281</v>
       </c>
       <c r="D87" t="s" s="9">
-        <v>306</v>
+        <v>282</v>
       </c>
       <c r="E87" t="s" s="9">
         <v>35</v>
       </c>
       <c r="F87" t="s" s="9">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="G87" t="s" s="9">
         <v>31</v>
       </c>
       <c r="H87" t="s" s="9">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="I87" t="s" s="9">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J87" t="s" s="9">
         <v>31</v>
@@ -5800,7 +5651,7 @@
       </c>
       <c r="N87" s="9"/>
       <c r="O87" t="s" s="10">
-        <v>307</v>
+        <v>283</v>
       </c>
     </row>
     <row r="88" ht="20.05" customHeight="1">
@@ -5809,7 +5660,7 @@
         <v>29</v>
       </c>
       <c r="C88" t="s" s="6">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
@@ -5828,10 +5679,10 @@
       <c r="A89" s="8"/>
       <c r="B89" s="9"/>
       <c r="C89" t="s" s="9">
-        <v>309</v>
+        <v>285</v>
       </c>
       <c r="D89" t="s" s="9">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="E89" t="s" s="9">
         <v>46</v>
@@ -5846,7 +5697,7 @@
         <v>64</v>
       </c>
       <c r="I89" t="s" s="9">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="J89" t="s" s="9">
         <v>31</v>
@@ -5860,21 +5711,19 @@
       <c r="M89" t="s" s="9">
         <v>62</v>
       </c>
-      <c r="N89" t="s" s="9">
-        <v>311</v>
-      </c>
+      <c r="N89" s="9"/>
       <c r="O89" t="s" s="10">
-        <v>312</v>
+        <v>287</v>
       </c>
     </row>
     <row r="90" ht="20.05" customHeight="1">
       <c r="A90" s="5"/>
       <c r="B90" s="6"/>
       <c r="C90" t="s" s="6">
-        <v>313</v>
+        <v>288</v>
       </c>
       <c r="D90" t="s" s="6">
-        <v>314</v>
+        <v>289</v>
       </c>
       <c r="E90" t="s" s="6">
         <v>46</v>
@@ -5886,10 +5735,10 @@
         <v>31</v>
       </c>
       <c r="H90" t="s" s="6">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="I90" t="s" s="6">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J90" t="s" s="6">
         <v>34</v>
@@ -5905,17 +5754,17 @@
       </c>
       <c r="N90" s="6"/>
       <c r="O90" t="s" s="7">
-        <v>315</v>
+        <v>290</v>
       </c>
     </row>
     <row r="91" ht="20.05" customHeight="1">
       <c r="A91" s="8"/>
       <c r="B91" s="9"/>
       <c r="C91" t="s" s="9">
-        <v>316</v>
+        <v>291</v>
       </c>
       <c r="D91" t="s" s="9">
-        <v>317</v>
+        <v>292</v>
       </c>
       <c r="E91" t="s" s="9">
         <v>46</v>
@@ -5927,10 +5776,10 @@
         <v>31</v>
       </c>
       <c r="H91" t="s" s="9">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="I91" t="s" s="9">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J91" t="s" s="9">
         <v>34</v>
@@ -5946,17 +5795,17 @@
       </c>
       <c r="N91" s="9"/>
       <c r="O91" t="s" s="10">
-        <v>318</v>
+        <v>293</v>
       </c>
     </row>
     <row r="92" ht="20.05" customHeight="1">
       <c r="A92" s="5"/>
       <c r="B92" s="6"/>
       <c r="C92" t="s" s="6">
-        <v>319</v>
+        <v>294</v>
       </c>
       <c r="D92" t="s" s="6">
-        <v>320</v>
+        <v>295</v>
       </c>
       <c r="E92" t="s" s="6">
         <v>46</v>
@@ -5968,10 +5817,10 @@
         <v>31</v>
       </c>
       <c r="H92" t="s" s="6">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="I92" t="s" s="6">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="J92" t="s" s="6">
         <v>31</v>
@@ -5987,7 +5836,7 @@
       </c>
       <c r="N92" s="6"/>
       <c r="O92" t="s" s="7">
-        <v>321</v>
+        <v>296</v>
       </c>
     </row>
     <row r="93" ht="20.05" customHeight="1">
@@ -5996,7 +5845,7 @@
         <v>29</v>
       </c>
       <c r="C93" t="s" s="9">
-        <v>322</v>
+        <v>297</v>
       </c>
       <c r="D93" s="9"/>
       <c r="E93" s="9"/>
@@ -6015,22 +5864,22 @@
       <c r="A94" s="5"/>
       <c r="B94" s="6"/>
       <c r="C94" t="s" s="6">
-        <v>323</v>
+        <v>298</v>
       </c>
       <c r="D94" t="s" s="6">
-        <v>324</v>
+        <v>299</v>
       </c>
       <c r="E94" t="s" s="6">
         <v>58</v>
       </c>
       <c r="F94" t="s" s="6">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="G94" t="s" s="6">
         <v>31</v>
       </c>
       <c r="H94" t="s" s="6">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I94" t="s" s="6">
         <v>86</v>
@@ -6047,36 +5896,34 @@
       <c r="M94" t="s" s="6">
         <v>59</v>
       </c>
-      <c r="N94" t="s" s="6">
-        <v>325</v>
-      </c>
+      <c r="N94" s="6"/>
       <c r="O94" t="s" s="7">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="95" ht="20.05" customHeight="1">
       <c r="A95" s="8"/>
       <c r="B95" s="9"/>
       <c r="C95" t="s" s="9">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="D95" t="s" s="9">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="E95" t="s" s="9">
         <v>58</v>
       </c>
       <c r="F95" t="s" s="9">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="G95" t="s" s="9">
         <v>31</v>
       </c>
       <c r="H95" t="s" s="9">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I95" t="s" s="9">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J95" t="s" s="9">
         <v>31</v>
@@ -6092,17 +5939,17 @@
       </c>
       <c r="N95" s="9"/>
       <c r="O95" t="s" s="10">
-        <v>329</v>
+        <v>303</v>
       </c>
     </row>
     <row r="96" ht="20.05" customHeight="1">
       <c r="A96" s="5"/>
       <c r="B96" s="6"/>
       <c r="C96" t="s" s="6">
-        <v>330</v>
+        <v>304</v>
       </c>
       <c r="D96" t="s" s="6">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="E96" t="s" s="6">
         <v>58</v>
@@ -6114,10 +5961,10 @@
         <v>31</v>
       </c>
       <c r="H96" t="s" s="6">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I96" t="s" s="6">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J96" t="s" s="6">
         <v>31</v>
@@ -6131,36 +5978,34 @@
       <c r="M96" t="s" s="6">
         <v>59</v>
       </c>
-      <c r="N96" t="s" s="6">
-        <v>332</v>
-      </c>
+      <c r="N96" s="6"/>
       <c r="O96" t="s" s="7">
-        <v>333</v>
+        <v>306</v>
       </c>
     </row>
     <row r="97" ht="20.05" customHeight="1">
       <c r="A97" s="8"/>
       <c r="B97" s="9"/>
       <c r="C97" t="s" s="9">
-        <v>334</v>
+        <v>307</v>
       </c>
       <c r="D97" t="s" s="9">
-        <v>335</v>
+        <v>308</v>
       </c>
       <c r="E97" t="s" s="9">
         <v>58</v>
       </c>
       <c r="F97" t="s" s="9">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="G97" t="s" s="9">
         <v>31</v>
       </c>
       <c r="H97" t="s" s="9">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I97" t="s" s="9">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="J97" t="s" s="9">
         <v>31</v>
@@ -6176,7 +6021,7 @@
       </c>
       <c r="N97" s="9"/>
       <c r="O97" t="s" s="10">
-        <v>336</v>
+        <v>309</v>
       </c>
     </row>
     <row r="98" ht="20.05" customHeight="1">
@@ -6185,7 +6030,7 @@
         <v>29</v>
       </c>
       <c r="C98" t="s" s="6">
-        <v>337</v>
+        <v>310</v>
       </c>
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
@@ -6204,25 +6049,25 @@
       <c r="A99" s="8"/>
       <c r="B99" s="9"/>
       <c r="C99" t="s" s="9">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="D99" t="s" s="9">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="E99" t="s" s="9">
         <v>42</v>
       </c>
       <c r="F99" t="s" s="9">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="G99" t="s" s="9">
         <v>31</v>
       </c>
       <c r="H99" t="s" s="9">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="I99" t="s" s="9">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="J99" t="s" s="9">
         <v>31</v>
@@ -6236,36 +6081,34 @@
       <c r="M99" t="s" s="9">
         <v>52</v>
       </c>
-      <c r="N99" t="s" s="9">
-        <v>340</v>
-      </c>
+      <c r="N99" s="9"/>
       <c r="O99" t="s" s="10">
-        <v>341</v>
+        <v>313</v>
       </c>
     </row>
     <row r="100" ht="20.05" customHeight="1">
       <c r="A100" s="5"/>
       <c r="B100" s="6"/>
       <c r="C100" t="s" s="6">
-        <v>342</v>
+        <v>314</v>
       </c>
       <c r="D100" t="s" s="6">
-        <v>343</v>
+        <v>315</v>
       </c>
       <c r="E100" t="s" s="6">
         <v>42</v>
       </c>
       <c r="F100" t="s" s="6">
-        <v>344</v>
+        <v>316</v>
       </c>
       <c r="G100" t="s" s="6">
         <v>31</v>
       </c>
       <c r="H100" t="s" s="6">
-        <v>345</v>
+        <v>317</v>
       </c>
       <c r="I100" t="s" s="6">
-        <v>346</v>
+        <v>318</v>
       </c>
       <c r="J100" t="s" s="6">
         <v>34</v>
@@ -6281,23 +6124,23 @@
       </c>
       <c r="N100" s="6"/>
       <c r="O100" t="s" s="7">
-        <v>347</v>
+        <v>319</v>
       </c>
     </row>
     <row r="101" ht="20.05" customHeight="1">
       <c r="A101" s="8"/>
       <c r="B101" s="9"/>
       <c r="C101" t="s" s="9">
-        <v>348</v>
+        <v>320</v>
       </c>
       <c r="D101" t="s" s="9">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="E101" t="s" s="9">
         <v>42</v>
       </c>
       <c r="F101" t="s" s="9">
-        <v>350</v>
+        <v>322</v>
       </c>
       <c r="G101" t="s" s="9">
         <v>31</v>
@@ -6306,7 +6149,7 @@
         <v>34</v>
       </c>
       <c r="I101" t="s" s="9">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="J101" t="s" s="9">
         <v>34</v>
@@ -6322,7 +6165,7 @@
       </c>
       <c r="N101" s="9"/>
       <c r="O101" t="s" s="10">
-        <v>351</v>
+        <v>323</v>
       </c>
     </row>
     <row r="102" ht="20.05" customHeight="1">
@@ -6331,7 +6174,7 @@
         <v>29</v>
       </c>
       <c r="C102" t="s" s="6">
-        <v>352</v>
+        <v>324</v>
       </c>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
@@ -6350,25 +6193,25 @@
       <c r="A103" s="8"/>
       <c r="B103" s="9"/>
       <c r="C103" t="s" s="9">
-        <v>353</v>
+        <v>325</v>
       </c>
       <c r="D103" t="s" s="9">
-        <v>354</v>
+        <v>326</v>
       </c>
       <c r="E103" t="s" s="9">
         <v>56</v>
       </c>
       <c r="F103" t="s" s="9">
-        <v>344</v>
+        <v>316</v>
       </c>
       <c r="G103" t="s" s="9">
         <v>31</v>
       </c>
       <c r="H103" t="s" s="9">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="I103" t="s" s="9">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J103" t="s" s="9">
         <v>31</v>
@@ -6382,52 +6225,50 @@
       <c r="M103" t="s" s="9">
         <v>36</v>
       </c>
-      <c r="N103" t="s" s="9">
-        <v>355</v>
-      </c>
+      <c r="N103" s="9"/>
       <c r="O103" t="s" s="10">
-        <v>356</v>
+        <v>327</v>
       </c>
     </row>
     <row r="104" ht="20.05" customHeight="1">
-      <c r="A104" s="12"/>
-      <c r="B104" s="13"/>
-      <c r="C104" t="s" s="13">
-        <v>357</v>
-      </c>
-      <c r="D104" t="s" s="13">
-        <v>358</v>
-      </c>
-      <c r="E104" t="s" s="13">
+      <c r="A104" s="14"/>
+      <c r="B104" s="15"/>
+      <c r="C104" t="s" s="15">
+        <v>328</v>
+      </c>
+      <c r="D104" t="s" s="15">
+        <v>329</v>
+      </c>
+      <c r="E104" t="s" s="15">
         <v>56</v>
       </c>
-      <c r="F104" t="s" s="13">
-        <v>350</v>
-      </c>
-      <c r="G104" t="s" s="13">
-        <v>31</v>
-      </c>
-      <c r="H104" t="s" s="13">
-        <v>34</v>
-      </c>
-      <c r="I104" t="s" s="13">
-        <v>259</v>
-      </c>
-      <c r="J104" t="s" s="13">
-        <v>34</v>
-      </c>
-      <c r="K104" t="s" s="13">
-        <v>34</v>
-      </c>
-      <c r="L104" t="s" s="13">
-        <v>34</v>
-      </c>
-      <c r="M104" t="s" s="13">
-        <v>34</v>
-      </c>
-      <c r="N104" s="13"/>
-      <c r="O104" t="s" s="14">
-        <v>359</v>
+      <c r="F104" t="s" s="15">
+        <v>322</v>
+      </c>
+      <c r="G104" t="s" s="15">
+        <v>31</v>
+      </c>
+      <c r="H104" t="s" s="15">
+        <v>34</v>
+      </c>
+      <c r="I104" t="s" s="15">
+        <v>238</v>
+      </c>
+      <c r="J104" t="s" s="15">
+        <v>34</v>
+      </c>
+      <c r="K104" t="s" s="15">
+        <v>34</v>
+      </c>
+      <c r="L104" t="s" s="15">
+        <v>34</v>
+      </c>
+      <c r="M104" t="s" s="15">
+        <v>34</v>
+      </c>
+      <c r="N104" s="15"/>
+      <c r="O104" t="s" s="16">
+        <v>330</v>
       </c>
     </row>
   </sheetData>
